--- a/OrganizedData/Youngs_Modulus_Results/Youngs_Modulus_Yearly_Summary.xlsx
+++ b/OrganizedData/Youngs_Modulus_Results/Youngs_Modulus_Yearly_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="56" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="16">
   <si>
     <t>Year</t>
   </si>
@@ -110,14 +110,14 @@
   <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.90625" customWidth="true"/>
-    <col min="2" max="2" width="7.90625" customWidth="true"/>
-    <col min="3" max="3" width="11.81640625" customWidth="true"/>
-    <col min="4" max="4" width="23.81640625" customWidth="true"/>
-    <col min="5" max="5" width="21.08984375" customWidth="true"/>
-    <col min="6" max="6" width="18.54296875" customWidth="true"/>
-    <col min="7" max="7" width="27.08984375" customWidth="true"/>
-    <col min="8" max="8" width="27.453125" customWidth="true"/>
+    <col min="1" max="1" width="5.140625" customWidth="true"/>
+    <col min="2" max="2" width="8.5703125" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="25" customWidth="true"/>
+    <col min="5" max="5" width="22.42578125" customWidth="true"/>
+    <col min="6" max="6" width="20.140625" customWidth="true"/>
+    <col min="7" max="7" width="28.5703125" customWidth="true"/>
+    <col min="8" max="8" width="28.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -157,7 +157,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="0">
-        <v>751.32609006979556</v>
+        <v>751.32609006979567</v>
       </c>
       <c r="E2" s="0">
         <v>526.41974017603059</v>
@@ -166,10 +166,10 @@
         <v>10</v>
       </c>
       <c r="G2" s="0">
-        <v>36.968752859095488</v>
+        <v>36.968752859095495</v>
       </c>
       <c r="H2" s="0">
-        <v>1577.5282337380456</v>
+        <v>1577.5282337380461</v>
       </c>
     </row>
     <row r="3">
@@ -183,10 +183,10 @@
         <v>10</v>
       </c>
       <c r="D3" s="0">
-        <v>2211.7026873113514</v>
+        <v>2211.7026873113509</v>
       </c>
       <c r="E3" s="0">
-        <v>463.65552882015743</v>
+        <v>463.6555288201576</v>
       </c>
       <c r="F3" s="0">
         <v>10</v>
@@ -209,19 +209,19 @@
         <v>9</v>
       </c>
       <c r="D4" s="0">
-        <v>752.24881984366243</v>
+        <v>752.24881984366266</v>
       </c>
       <c r="E4" s="0">
-        <v>496.76198920727529</v>
+        <v>496.76198920727552</v>
       </c>
       <c r="F4" s="0">
         <v>8</v>
       </c>
       <c r="G4" s="0">
-        <v>30.482339810018175</v>
+        <v>30.482339810018182</v>
       </c>
       <c r="H4" s="0">
-        <v>1734.3440438348966</v>
+        <v>1734.3440438348973</v>
       </c>
     </row>
     <row r="5">
@@ -261,7 +261,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="0">
-        <v>1485.822001736188</v>
+        <v>1485.8220017361878</v>
       </c>
       <c r="E6" s="0">
         <v>668.3535416141508</v>
@@ -287,10 +287,10 @@
         <v>10</v>
       </c>
       <c r="D7" s="0">
-        <v>2030.4851340229181</v>
+        <v>2030.4851340229177</v>
       </c>
       <c r="E7" s="0">
-        <v>418.05619015961315</v>
+        <v>418.0561901596131</v>
       </c>
       <c r="F7" s="0">
         <v>25</v>
@@ -299,7 +299,7 @@
         <v>1200.264368055427</v>
       </c>
       <c r="H7" s="0">
-        <v>2833.3640217794336</v>
+        <v>2833.3640217794332</v>
       </c>
     </row>
     <row r="8">
@@ -313,7 +313,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="0">
-        <v>1349.4106228880644</v>
+        <v>1349.4106228880642</v>
       </c>
       <c r="E8" s="0">
         <v>475.39755155198378</v>
@@ -322,7 +322,7 @@
         <v>23</v>
       </c>
       <c r="G8" s="0">
-        <v>633.64562852100642</v>
+        <v>633.6456285210063</v>
       </c>
       <c r="H8" s="0">
         <v>2321.8906024914031</v>
@@ -348,10 +348,10 @@
         <v>22</v>
       </c>
       <c r="G9" s="0">
-        <v>1121.5213782616102</v>
+        <v>1121.5213782616097</v>
       </c>
       <c r="H9" s="0">
-        <v>2623.734741902274</v>
+        <v>2623.7347419022735</v>
       </c>
     </row>
     <row r="10">
@@ -365,10 +365,10 @@
         <v>9</v>
       </c>
       <c r="D10" s="0">
-        <v>1853.6345934387721</v>
+        <v>1853.6345934387723</v>
       </c>
       <c r="E10" s="0">
-        <v>571.27919132123236</v>
+        <v>571.27919132123225</v>
       </c>
       <c r="F10" s="0">
         <v>27</v>
@@ -391,16 +391,16 @@
         <v>10</v>
       </c>
       <c r="D11" s="0">
-        <v>2236.2659006920694</v>
+        <v>2236.2659006920699</v>
       </c>
       <c r="E11" s="0">
-        <v>658.06284149809267</v>
+        <v>658.06284149809278</v>
       </c>
       <c r="F11" s="0">
         <v>24</v>
       </c>
       <c r="G11" s="0">
-        <v>1056.3808174752112</v>
+        <v>1056.3808174752107</v>
       </c>
       <c r="H11" s="0">
         <v>3516.0982637308894</v>
@@ -420,7 +420,7 @@
         <v>1603.0002448229764</v>
       </c>
       <c r="E12" s="0">
-        <v>629.70410066461136</v>
+        <v>629.70410066461147</v>
       </c>
       <c r="F12" s="0">
         <v>23</v>
@@ -429,7 +429,7 @@
         <v>631.81106455336453</v>
       </c>
       <c r="H12" s="0">
-        <v>2555.8481455882634</v>
+        <v>2555.8481455882638</v>
       </c>
     </row>
     <row r="13">
@@ -443,7 +443,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="0">
-        <v>1989.3953721058765</v>
+        <v>1989.3953721058761</v>
       </c>
       <c r="E13" s="0">
         <v>531.17232783681538</v>
@@ -455,7 +455,7 @@
         <v>1389.3562190468283</v>
       </c>
       <c r="H13" s="0">
-        <v>2874.8707020139023</v>
+        <v>2874.8707020139027</v>
       </c>
     </row>
     <row r="14">
@@ -472,13 +472,13 @@
         <v>545.19885788220074</v>
       </c>
       <c r="E14" s="0">
-        <v>510.8976800778845</v>
+        <v>510.89768007788456</v>
       </c>
       <c r="F14" s="0">
         <v>21</v>
       </c>
       <c r="G14" s="0">
-        <v>3.3534192222269947</v>
+        <v>3.3534192222269978</v>
       </c>
       <c r="H14" s="0">
         <v>1596.719801752577</v>
@@ -524,7 +524,7 @@
         <v>356.70263986058626</v>
       </c>
       <c r="E16" s="0">
-        <v>250.12753728821039</v>
+        <v>250.12753728821036</v>
       </c>
       <c r="F16" s="0">
         <v>19</v>
@@ -550,7 +550,7 @@
         <v>1413.4738196570427</v>
       </c>
       <c r="E17" s="0">
-        <v>440.97784790612263</v>
+        <v>440.97784790612246</v>
       </c>
       <c r="F17" s="0">
         <v>17</v>
@@ -559,7 +559,7 @@
         <v>715.94355330175108</v>
       </c>
       <c r="H17" s="0">
-        <v>2269.1203856965349</v>
+        <v>2269.1203856965344</v>
       </c>
     </row>
   </sheetData>

--- a/OrganizedData/Youngs_Modulus_Results/Youngs_Modulus_Yearly_Summary.xlsx
+++ b/OrganizedData/Youngs_Modulus_Results/Youngs_Modulus_Yearly_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1232" uniqueCount="16">
   <si>
     <t>Year</t>
   </si>
@@ -157,19 +157,19 @@
         <v>9</v>
       </c>
       <c r="D2" s="0">
-        <v>751.32609006979567</v>
+        <v>894.65309383355509</v>
       </c>
       <c r="E2" s="0">
-        <v>526.41974017603059</v>
+        <v>582.67435003944149</v>
       </c>
       <c r="F2" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" s="0">
         <v>36.968752859095495</v>
       </c>
       <c r="H2" s="0">
-        <v>1577.5282337380461</v>
+        <v>1674.477882536188</v>
       </c>
     </row>
     <row r="3">
@@ -183,19 +183,19 @@
         <v>10</v>
       </c>
       <c r="D3" s="0">
-        <v>2211.7026873113509</v>
+        <v>2419.6887328021676</v>
       </c>
       <c r="E3" s="0">
-        <v>463.6555288201576</v>
+        <v>2032.0877215082894</v>
       </c>
       <c r="F3" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G3" s="0">
-        <v>1379.1555370340957</v>
+        <v>183.26602340994526</v>
       </c>
       <c r="H3" s="0">
-        <v>2872.2984253392528</v>
+        <v>8587.1824640422892</v>
       </c>
     </row>
     <row r="4">
@@ -209,19 +209,19 @@
         <v>9</v>
       </c>
       <c r="D4" s="0">
-        <v>752.24881984366266</v>
+        <v>943.79095627685649</v>
       </c>
       <c r="E4" s="0">
-        <v>496.76198920727552</v>
+        <v>727.43999630527708</v>
       </c>
       <c r="F4" s="0">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G4" s="0">
         <v>30.482339810018182</v>
       </c>
       <c r="H4" s="0">
-        <v>1734.3440438348973</v>
+        <v>2711.2956333777684</v>
       </c>
     </row>
     <row r="5">
@@ -235,19 +235,19 @@
         <v>10</v>
       </c>
       <c r="D5" s="0">
-        <v>1906.164545581333</v>
+        <v>1890.9430052512096</v>
       </c>
       <c r="E5" s="0">
-        <v>305.7739157306861</v>
+        <v>1430.6207398967433</v>
       </c>
       <c r="F5" s="0">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5" s="0">
-        <v>1563.9250284165958</v>
+        <v>174.39749213771449</v>
       </c>
       <c r="H5" s="0">
-        <v>2415.2258923459131</v>
+        <v>6230.7485354392111</v>
       </c>
     </row>
     <row r="6">
@@ -261,13 +261,13 @@
         <v>9</v>
       </c>
       <c r="D6" s="0">
-        <v>1485.8220017361878</v>
+        <v>1497.7283231320312</v>
       </c>
       <c r="E6" s="0">
-        <v>668.3535416141508</v>
+        <v>650.54340021047585</v>
       </c>
       <c r="F6" s="0">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G6" s="0">
         <v>92.492101504928812</v>
@@ -287,19 +287,19 @@
         <v>10</v>
       </c>
       <c r="D7" s="0">
-        <v>2030.4851340229177</v>
+        <v>2433.4687605223007</v>
       </c>
       <c r="E7" s="0">
-        <v>418.0561901596131</v>
+        <v>1506.8328974415263</v>
       </c>
       <c r="F7" s="0">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G7" s="0">
         <v>1200.264368055427</v>
       </c>
       <c r="H7" s="0">
-        <v>2833.3640217794332</v>
+        <v>7595.4493695615765</v>
       </c>
     </row>
     <row r="8">
@@ -313,13 +313,13 @@
         <v>9</v>
       </c>
       <c r="D8" s="0">
-        <v>1349.4106228880642</v>
+        <v>1339.10482831997</v>
       </c>
       <c r="E8" s="0">
-        <v>475.39755155198378</v>
+        <v>458.41784772427297</v>
       </c>
       <c r="F8" s="0">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G8" s="0">
         <v>633.6456285210063</v>
@@ -339,19 +339,19 @@
         <v>10</v>
       </c>
       <c r="D9" s="0">
-        <v>1742.4506378410611</v>
+        <v>2036.4986909364745</v>
       </c>
       <c r="E9" s="0">
-        <v>372.70908761740316</v>
+        <v>1097.694790859571</v>
       </c>
       <c r="F9" s="0">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G9" s="0">
         <v>1121.5213782616097</v>
       </c>
       <c r="H9" s="0">
-        <v>2623.7347419022735</v>
+        <v>6263.4388095046643</v>
       </c>
     </row>
     <row r="10">
@@ -365,13 +365,13 @@
         <v>9</v>
       </c>
       <c r="D10" s="0">
-        <v>1853.6345934387723</v>
+        <v>1802.6798838174036</v>
       </c>
       <c r="E10" s="0">
-        <v>571.27919132123225</v>
+        <v>583.76835868834996</v>
       </c>
       <c r="F10" s="0">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G10" s="0">
         <v>948.94148391356703</v>
@@ -417,16 +417,16 @@
         <v>9</v>
       </c>
       <c r="D12" s="0">
-        <v>1603.0002448229764</v>
+        <v>1476.645600007304</v>
       </c>
       <c r="E12" s="0">
-        <v>629.70410066461147</v>
+        <v>694.91402885713819</v>
       </c>
       <c r="F12" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G12" s="0">
-        <v>631.81106455336453</v>
+        <v>185.20146615966465</v>
       </c>
       <c r="H12" s="0">
         <v>2555.8481455882638</v>
@@ -443,19 +443,19 @@
         <v>10</v>
       </c>
       <c r="D13" s="0">
-        <v>1989.3953721058761</v>
+        <v>2185.7407957648179</v>
       </c>
       <c r="E13" s="0">
-        <v>531.17232783681538</v>
+        <v>561.31909173448548</v>
       </c>
       <c r="F13" s="0">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="G13" s="0">
         <v>1389.3562190468283</v>
       </c>
       <c r="H13" s="0">
-        <v>2874.8707020139027</v>
+        <v>3457.4179991622918</v>
       </c>
     </row>
     <row r="14">
@@ -495,19 +495,19 @@
         <v>10</v>
       </c>
       <c r="D15" s="0">
-        <v>1833.8349726341053</v>
+        <v>2378.8465233068355</v>
       </c>
       <c r="E15" s="0">
-        <v>647.7297301241714</v>
+        <v>1855.4167606498543</v>
       </c>
       <c r="F15" s="0">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G15" s="0">
         <v>942.14662656429948</v>
       </c>
       <c r="H15" s="0">
-        <v>3273.6627763292699</v>
+        <v>9246.4293272973719</v>
       </c>
     </row>
     <row r="16">
@@ -547,19 +547,19 @@
         <v>10</v>
       </c>
       <c r="D17" s="0">
-        <v>1413.4738196570427</v>
+        <v>1945.4105146021836</v>
       </c>
       <c r="E17" s="0">
-        <v>440.97784790612246</v>
+        <v>1897.602167497897</v>
       </c>
       <c r="F17" s="0">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G17" s="0">
-        <v>715.94355330175108</v>
+        <v>325.63662591444853</v>
       </c>
       <c r="H17" s="0">
-        <v>2269.1203856965344</v>
+        <v>8818.9114330156663</v>
       </c>
     </row>
   </sheetData>
